--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2023_nuble.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:56</t>
+    <t xml:space="preserve">2026-09-24 01:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -845,13 +845,13 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.21</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>328</v>
@@ -868,19 +868,19 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.21</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="18">
